--- a/research/traditional_assets/database/data/netherlands/netherlands_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_green_renewable_energy.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,8 +587,23 @@
           <t>Green &amp; Renewable Energy</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-1.156</v>
+      </c>
+      <c r="H2">
+        <v>-1.156</v>
+      </c>
+      <c r="I2">
+        <v>-1.548</v>
+      </c>
+      <c r="J2">
+        <v>-1.548</v>
+      </c>
       <c r="K2">
-        <v>-0.153</v>
+        <v>-4.06</v>
+      </c>
+      <c r="L2">
+        <v>-1.624</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,61 +627,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.006</v>
+        <v>26.1</v>
       </c>
       <c r="V2">
-        <v>0.001680672268907563</v>
-      </c>
-      <c r="W2">
-        <v>0.2417061611374408</v>
+        <v>0.821529745042493</v>
       </c>
       <c r="X2">
-        <v>0.04548259785896581</v>
-      </c>
-      <c r="Y2">
-        <v>0.196223563278475</v>
+        <v>0.106890909594716</v>
       </c>
       <c r="Z2">
-        <v>-0</v>
-      </c>
-      <c r="AA2">
-        <v>1.945205479452054</v>
+        <v>0.2155172413793102</v>
       </c>
       <c r="AB2">
-        <v>0.04548259785896581</v>
-      </c>
-      <c r="AC2">
-        <v>1.899722881593088</v>
+        <v>0.07998655700635215</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>41.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>41.4</v>
       </c>
       <c r="AG2">
-        <v>-0.006</v>
+        <v>15.3</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.5658056580565806</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.3496621621621621</v>
       </c>
       <c r="AJ2">
-        <v>-0.001683501683501683</v>
+        <v>0.3250478011472275</v>
       </c>
       <c r="AK2">
-        <v>-0.07058823529411766</v>
+        <v>0.1657638136511376</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.431</v>
+      </c>
+      <c r="AN2">
+        <v>-17.61702127659574</v>
+      </c>
+      <c r="AO2">
+        <v>-552.8571428571429</v>
+      </c>
+      <c r="AP2">
+        <v>-6.510638297872339</v>
+      </c>
+      <c r="AQ2">
+        <v>8.979118329466358</v>
       </c>
     </row>
     <row r="3">
@@ -677,93 +692,197 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>MPC Energy Solutions N.V. (OB:MPCES)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Green &amp; Renewable Energy</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>-1.156</v>
+      </c>
+      <c r="H3">
+        <v>-1.156</v>
+      </c>
+      <c r="I3">
+        <v>-1.508</v>
+      </c>
+      <c r="J3">
+        <v>-1.508</v>
+      </c>
+      <c r="K3">
+        <v>-3.96</v>
+      </c>
+      <c r="L3">
+        <v>-1.584</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>26.1</v>
+      </c>
+      <c r="V3">
+        <v>0.9321428571428572</v>
+      </c>
+      <c r="W3">
+        <v>-0.04731182795698925</v>
+      </c>
+      <c r="X3">
+        <v>0.131011066165819</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1783228941228082</v>
+      </c>
+      <c r="Z3">
+        <v>0.2155172413793102</v>
+      </c>
+      <c r="AA3">
+        <v>-0.3249999999999998</v>
+      </c>
+      <c r="AB3">
+        <v>0.07720236098909124</v>
+      </c>
+      <c r="AC3">
+        <v>-0.402202360989091</v>
+      </c>
+      <c r="AD3">
+        <v>41.4</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>41.4</v>
+      </c>
+      <c r="AG3">
+        <v>15.3</v>
+      </c>
+      <c r="AH3">
+        <v>0.5965417867435158</v>
+      </c>
+      <c r="AI3">
+        <v>0.3496621621621621</v>
+      </c>
+      <c r="AJ3">
+        <v>0.3533487297921478</v>
+      </c>
+      <c r="AK3">
+        <v>0.1657638136511376</v>
+      </c>
+      <c r="AL3">
+        <v>0.007</v>
+      </c>
+      <c r="AM3">
+        <v>-0.431</v>
+      </c>
+      <c r="AN3">
+        <v>-17.61702127659574</v>
+      </c>
+      <c r="AO3">
+        <v>-538.5714285714286</v>
+      </c>
+      <c r="AP3">
+        <v>-6.510638297872339</v>
+      </c>
+      <c r="AQ3">
+        <v>8.747099767981439</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>New Sources Energy N.V. (ENXTAM:NSE)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Green &amp; Renewable Energy</t>
         </is>
       </c>
-      <c r="K3">
-        <v>-0.153</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.006</v>
-      </c>
-      <c r="V3">
-        <v>0.001680672268907563</v>
-      </c>
-      <c r="W3">
-        <v>0.2417061611374408</v>
-      </c>
-      <c r="X3">
-        <v>0.04548259785896581</v>
-      </c>
-      <c r="Y3">
-        <v>0.196223563278475</v>
-      </c>
-      <c r="Z3">
-        <v>-0</v>
-      </c>
-      <c r="AA3">
-        <v>1.945205479452054</v>
-      </c>
-      <c r="AB3">
-        <v>0.04548259785896581</v>
-      </c>
-      <c r="AC3">
-        <v>1.899722881593088</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>-0.006</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.001683501683501683</v>
-      </c>
-      <c r="AK3">
-        <v>-0.07058823529411766</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="K4">
+        <v>-0.1</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0.08277075302361306</v>
+      </c>
+      <c r="AB4">
+        <v>0.08277075302361306</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/netherlands/netherlands_green_renewable_energy.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_green_renewable_energy.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-1.156</v>
+        <v>-0.2656641604010025</v>
       </c>
       <c r="H2">
-        <v>-1.156</v>
+        <v>-0.2656641604010025</v>
       </c>
       <c r="I2">
-        <v>-1.548</v>
+        <v>-0.6206766917293233</v>
       </c>
       <c r="J2">
-        <v>-1.548</v>
+        <v>-0.6206766917293233</v>
       </c>
       <c r="K2">
-        <v>-4.06</v>
+        <v>-7.038</v>
       </c>
       <c r="L2">
-        <v>-1.624</v>
+        <v>-0.881954887218045</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,61 +627,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>26.1</v>
+        <v>13.1</v>
       </c>
       <c r="V2">
-        <v>0.821529745042493</v>
+        <v>0.4886236478925773</v>
       </c>
       <c r="X2">
-        <v>0.106890909594716</v>
+        <v>0.08453437842004938</v>
       </c>
       <c r="Z2">
-        <v>0.2155172413793102</v>
+        <v>0.08713122092896293</v>
       </c>
       <c r="AB2">
-        <v>0.07998655700635215</v>
+        <v>0.06135160468814377</v>
       </c>
       <c r="AD2">
-        <v>41.4</v>
+        <v>45.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>41.4</v>
+        <v>45.8</v>
       </c>
       <c r="AG2">
-        <v>15.3</v>
+        <v>32.7</v>
       </c>
       <c r="AH2">
-        <v>0.5658056580565806</v>
+        <v>0.6307671119680485</v>
       </c>
       <c r="AI2">
-        <v>0.3496621621621621</v>
+        <v>0.3823038397328881</v>
       </c>
       <c r="AJ2">
-        <v>0.3250478011472275</v>
+        <v>0.5494874810956142</v>
       </c>
       <c r="AK2">
-        <v>0.1657638136511376</v>
+        <v>0.3064667291471415</v>
       </c>
       <c r="AL2">
-        <v>0.007</v>
+        <v>2.775</v>
       </c>
       <c r="AM2">
-        <v>-0.431</v>
+        <v>2.392</v>
       </c>
       <c r="AN2">
-        <v>-17.61702127659574</v>
+        <v>-32.71428571428572</v>
       </c>
       <c r="AO2">
-        <v>-552.8571428571429</v>
+        <v>-1.784864864864865</v>
       </c>
       <c r="AP2">
-        <v>-6.510638297872339</v>
+        <v>-23.35714285714285</v>
       </c>
       <c r="AQ2">
-        <v>8.979118329466358</v>
+        <v>-2.070652173913044</v>
       </c>
     </row>
     <row r="3">
@@ -701,22 +701,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-1.156</v>
+        <v>-0.2656641604010025</v>
       </c>
       <c r="H3">
-        <v>-1.156</v>
+        <v>-0.2656641604010025</v>
       </c>
       <c r="I3">
-        <v>-1.508</v>
+        <v>-0.6090225563909775</v>
       </c>
       <c r="J3">
-        <v>-1.508</v>
+        <v>-0.6090225563909775</v>
       </c>
       <c r="K3">
-        <v>-3.96</v>
+        <v>-6.94</v>
       </c>
       <c r="L3">
-        <v>-1.584</v>
+        <v>-0.8696741854636592</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,73 +740,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>26.1</v>
+        <v>13.1</v>
       </c>
       <c r="V3">
-        <v>0.9321428571428572</v>
+        <v>0.5550847457627118</v>
       </c>
       <c r="W3">
-        <v>-0.04731182795698925</v>
+        <v>-0.09071895424836601</v>
       </c>
       <c r="X3">
-        <v>0.131011066165819</v>
+        <v>0.1036788709342467</v>
       </c>
       <c r="Y3">
-        <v>-0.1783228941228082</v>
+        <v>-0.1943978251826127</v>
       </c>
       <c r="Z3">
-        <v>0.2155172413793102</v>
+        <v>0.08713122092896293</v>
       </c>
       <c r="AA3">
-        <v>-0.3249999999999998</v>
+        <v>-0.05306487891162404</v>
       </c>
       <c r="AB3">
-        <v>0.07720236098909124</v>
+        <v>0.05731332347043548</v>
       </c>
       <c r="AC3">
-        <v>-0.402202360989091</v>
+        <v>-0.1103782023820595</v>
       </c>
       <c r="AD3">
-        <v>41.4</v>
+        <v>45.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>41.4</v>
+        <v>45.8</v>
       </c>
       <c r="AG3">
-        <v>15.3</v>
+        <v>32.7</v>
       </c>
       <c r="AH3">
-        <v>0.5965417867435158</v>
+        <v>0.6599423631123918</v>
       </c>
       <c r="AI3">
-        <v>0.3496621621621621</v>
+        <v>0.3823038397328881</v>
       </c>
       <c r="AJ3">
-        <v>0.3533487297921478</v>
+        <v>0.580817051509769</v>
       </c>
       <c r="AK3">
-        <v>0.1657638136511376</v>
+        <v>0.3064667291471415</v>
       </c>
       <c r="AL3">
-        <v>0.007</v>
+        <v>2.77</v>
       </c>
       <c r="AM3">
-        <v>-0.431</v>
+        <v>2.387</v>
       </c>
       <c r="AN3">
-        <v>-17.61702127659574</v>
+        <v>-32.71428571428572</v>
       </c>
       <c r="AO3">
-        <v>-538.5714285714286</v>
+        <v>-1.754512635379061</v>
       </c>
       <c r="AP3">
-        <v>-6.510638297872339</v>
+        <v>-23.35714285714285</v>
       </c>
       <c r="AQ3">
-        <v>8.747099767981439</v>
+        <v>-2.036028487641391</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="K4">
-        <v>-0.1</v>
+        <v>-0.098</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -856,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="X4">
-        <v>0.08277075302361306</v>
+        <v>0.06538988590585205</v>
       </c>
       <c r="AB4">
-        <v>0.08277075302361306</v>
+        <v>0.06538988590585205</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -880,10 +880,16 @@
         <v>0</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.005</v>
+      </c>
+      <c r="AO4">
+        <v>-18.6</v>
+      </c>
+      <c r="AQ4">
+        <v>-18.6</v>
       </c>
     </row>
   </sheetData>
